--- a/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>MYNZ</t>
   </si>
@@ -897,7 +897,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="E12" s="3">
         <v>3400</v>
@@ -990,8 +990,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>0</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1037,8 +1037,8 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>300</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1101,7 +1101,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="E17" s="3">
         <v>8200</v>
@@ -1148,7 +1148,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-5600</v>
+        <v>-5700</v>
       </c>
       <c r="E18" s="3">
         <v>-8000</v>
@@ -1214,7 +1214,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>-600</v>
       </c>
       <c r="E20" s="3">
         <v>-300</v>
@@ -1260,14 +1260,14 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-6100</v>
       </c>
       <c r="E21" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
+        <v>-8100</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-6300</v>
       </c>
       <c r="G21" s="3">
         <v>-13300</v>
@@ -1275,11 +1275,11 @@
       <c r="H21" s="3">
         <v>-12500</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="I21" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-200</v>
       </c>
       <c r="K21" s="3">
         <v>-400</v>
@@ -1778,7 +1778,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E32" s="3">
         <v>300</v>
@@ -2752,7 +2752,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3100</v>
+        <v>1500</v>
       </c>
       <c r="E57" s="3">
         <v>2700</v>
@@ -2846,7 +2846,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="E59" s="3">
         <v>2400</v>
@@ -2940,7 +2940,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2400</v>
+        <v>1400</v>
       </c>
       <c r="E61" s="3">
         <v>1600</v>
@@ -2987,7 +2987,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1800</v>
       </c>
       <c r="E62" s="3">
         <v>1900</v>
@@ -3828,26 +3828,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>500</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>300</v>
       </c>
       <c r="G83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
@@ -4110,26 +4110,26 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-6500</v>
       </c>
       <c r="E89" s="3">
-        <v>-10800</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
+        <v>-5100</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-5700</v>
       </c>
       <c r="G89" s="3">
-        <v>-14800</v>
+        <v>-8300</v>
       </c>
       <c r="H89" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="I89" s="3">
         <v>-3200</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="J89" s="3">
+        <v>-100</v>
       </c>
       <c r="K89" s="3">
         <v>-500</v>
@@ -4180,16 +4180,16 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -4317,26 +4317,26 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-1400</v>
       </c>
       <c r="G94" s="3">
-        <v>-700</v>
+        <v>-400</v>
       </c>
       <c r="H94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -4571,26 +4571,26 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>4600</v>
       </c>
       <c r="E100" s="3">
-        <v>6200</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
+        <v>5400</v>
+      </c>
+      <c r="F100" s="3">
+        <v>800</v>
       </c>
       <c r="G100" s="3">
-        <v>23900</v>
+        <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>13500</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>24100</v>
+      </c>
+      <c r="I100" s="3">
+        <v>10600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>200</v>
       </c>
       <c r="K100" s="3">
         <v>400</v>
@@ -4618,26 +4618,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>500</v>
       </c>
       <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4665,26 +4665,26 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-1600</v>
       </c>
       <c r="E102" s="3">
-        <v>-6200</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-6300</v>
       </c>
       <c r="G102" s="3">
-        <v>8400</v>
+        <v>-8900</v>
       </c>
       <c r="H102" s="3">
-        <v>8700</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>17300</v>
+      </c>
+      <c r="I102" s="3">
+        <v>8600</v>
+      </c>
+      <c r="J102" s="3">
+        <v>100</v>
       </c>
       <c r="K102" s="3">
         <v>-100</v>

--- a/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
@@ -656,69 +656,69 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -731,8 +731,11 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -743,29 +746,29 @@
         <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G8" s="3">
         <v>300</v>
       </c>
       <c r="H8" s="3">
+        <v>300</v>
+      </c>
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -778,8 +781,11 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -793,26 +799,26 @@
         <v>100</v>
       </c>
       <c r="G9" s="3">
+        <v>100</v>
+      </c>
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -825,8 +831,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -837,28 +846,28 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
+        <v>100</v>
+      </c>
+      <c r="G10" s="3">
         <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
       </c>
       <c r="I10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>200</v>
       </c>
       <c r="K10" s="3">
+        <v>200</v>
+      </c>
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
+      <c r="M10" s="3">
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
@@ -872,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,41 +903,42 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="3">
         <v>1700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2500</v>
       </c>
-      <c r="G12" s="3">
-        <v>2700</v>
-      </c>
       <c r="H12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,8 +951,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1001,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -999,26 +1018,26 @@
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1032,40 +1051,43 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1079,8 +1101,11 @@
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,41 +1120,42 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E17" s="3">
         <v>5900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,41 +1168,44 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-8000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,8 +1218,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,40 +1240,41 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1255,41 +1288,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-8100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-13300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="I21" s="3">
         <v>-12500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-11400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,13 +1338,16 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>600</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1316,27 +1355,27 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
+        <v>200</v>
+      </c>
+      <c r="I22" s="3">
         <v>100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
+        <v>200</v>
+      </c>
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="L22" s="3">
         <v>200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>100</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,41 +1388,44 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-8300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-13800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-11700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1396,8 +1438,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1437,14 +1482,17 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,41 +1538,44 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-8300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-13800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-11700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1537,41 +1588,44 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-8300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-13800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-11700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,8 +1638,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1672,14 +1732,17 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>3</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,40 +1838,43 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E32" s="3">
         <v>600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1819,41 +1888,44 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-8300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-13800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1866,8 +1938,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,41 +1988,44 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-8300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-13800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1960,46 +2038,49 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2012,8 +2093,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,35 +2135,36 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E41" s="3">
         <v>9300</v>
-      </c>
-      <c r="E41" s="3">
-        <v>10900</v>
       </c>
       <c r="F41" s="3">
         <v>10900</v>
       </c>
       <c r="G41" s="3">
+        <v>10900</v>
+      </c>
+      <c r="H41" s="3">
         <v>17100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2138,41 +2227,44 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>400</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
-      </c>
-      <c r="E43" s="3">
-        <v>400</v>
       </c>
       <c r="F43" s="3">
         <v>400</v>
       </c>
       <c r="G43" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,28 +2283,31 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
+      <c r="I44" s="3">
+        <v>0</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
@@ -2226,46 +2321,49 @@
       <c r="M44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
-      </c>
-      <c r="F45" s="3">
-        <v>800</v>
       </c>
       <c r="G45" s="3">
         <v>800</v>
       </c>
       <c r="H45" s="3">
+        <v>800</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2285,35 +2383,38 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E46" s="3">
         <v>11000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>26800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,8 +2433,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2373,41 +2477,44 @@
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3500</v>
       </c>
       <c r="F48" s="3">
         <v>3500</v>
       </c>
       <c r="G48" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H48" s="3">
         <v>1800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>500</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,23 +2533,26 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3700</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,8 +2565,8 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -2467,14 +2577,17 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,8 +2683,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2587,8 +2706,8 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3">
+        <v>0</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
@@ -2605,17 +2724,20 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,35 +2783,38 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E54" s="3">
         <v>17900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>700</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,35 +2875,36 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,25 +2923,28 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E58" s="3">
         <v>7800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
@@ -2819,8 +2952,8 @@
       <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>200</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -2840,35 +2973,38 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,35 +3023,38 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E60" s="3">
         <v>11300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2934,34 +3073,37 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>500</v>
-      </c>
-      <c r="I61" s="3">
-        <v>400</v>
       </c>
       <c r="J61" s="3">
         <v>400</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
@@ -2981,8 +3123,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2990,26 +3135,26 @@
         <v>1800</v>
       </c>
       <c r="E62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>900</v>
       </c>
       <c r="H62" s="3">
         <v>900</v>
       </c>
       <c r="I62" s="3">
+        <v>900</v>
+      </c>
+      <c r="J62" s="3">
         <v>1900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,35 +3323,38 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E66" s="3">
         <v>14500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3370,14 +3537,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3" t="s">
-        <v>3</v>
+      <c r="P70" s="3">
+        <v>0</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,35 +3593,38 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-43600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-38100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-30600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-25000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-14700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-6900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-2400</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,35 +3793,38 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E76" s="3">
         <v>3400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>14100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-2400</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,46 +3893,49 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3757,41 +3948,44 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-8300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-13800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3804,8 +3998,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,8 +4020,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3835,28 +4033,28 @@
         <v>200</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3870,8 +4068,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,41 +4318,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-5100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4152,8 +4368,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,29 +4390,30 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -4206,8 +4426,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -4218,8 +4438,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,40 +4538,43 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
       <c r="F94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -4359,8 +4588,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,40 +4808,43 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E100" s="3">
         <v>4600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3">
+        <v>0</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
@@ -4613,29 +4858,32 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
@@ -4645,8 +4893,8 @@
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4660,40 +4908,43 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>8600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>100</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-100</v>
       </c>
       <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>-100</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -4705,6 +4956,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>MYNZ</t>
   </si>
@@ -656,75 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -734,47 +736,53 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E8" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F8" s="3">
         <v>200</v>
       </c>
       <c r="G8" s="3">
+        <v>200</v>
+      </c>
+      <c r="H8" s="3">
+        <v>200</v>
+      </c>
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
-        <v>300</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3">
         <v>600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -784,8 +792,14 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -802,16 +816,16 @@
         <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L9" s="3">
         <v>400</v>
@@ -819,11 +833,11 @@
       <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="N9" s="3">
+        <v>400</v>
+      </c>
+      <c r="O9" s="3">
+        <v>200</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
@@ -834,22 +848,28 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F10" s="3">
         <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -858,22 +878,22 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
@@ -884,8 +904,14 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,46 +930,48 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E12" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="F12" s="3">
-        <v>3400</v>
+        <v>2000</v>
       </c>
       <c r="G12" s="3">
-        <v>2500</v>
+        <v>1900</v>
       </c>
       <c r="H12" s="3">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I12" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J12" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K12" s="3">
         <v>900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>300</v>
       </c>
       <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
+      <c r="N12" s="3">
+        <v>300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>100</v>
       </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
@@ -954,8 +982,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,22 +1038,28 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+        <v>-700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -1027,23 +1067,23 @@
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1054,8 +1094,14 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1063,25 +1109,25 @@
         <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
       </c>
       <c r="G15" s="3">
+        <v>100</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
         <v>200</v>
       </c>
-      <c r="H15" s="3">
-        <v>200</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>100</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1089,11 +1135,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
+      <c r="N15" s="3">
+        <v>100</v>
+      </c>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
@@ -1104,8 +1150,14 @@
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,47 +1173,49 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F17" s="3">
         <v>6800</v>
       </c>
-      <c r="E17" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H17" s="3">
         <v>8200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
-        <v>14200</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
+        <v>8600</v>
+      </c>
+      <c r="K17" s="3">
         <v>12800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>12300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,46 +1225,52 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-6600</v>
       </c>
-      <c r="E18" s="3">
-        <v>-5700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-8000</v>
-      </c>
       <c r="G18" s="3">
-        <v>-6400</v>
+        <v>-5600</v>
       </c>
       <c r="H18" s="3">
-        <v>-13900</v>
+        <v>-7900</v>
       </c>
       <c r="I18" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-12600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-700</v>
       </c>
       <c r="M18" s="3">
         <v>-300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="N18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-300</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1221,8 +1281,14 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,22 +1307,24 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-300</v>
+        <v>-1300</v>
       </c>
       <c r="G20" s="3">
-        <v>-200</v>
+        <v>700</v>
       </c>
       <c r="H20" s="3">
         <v>300</v>
@@ -1265,7 +1333,7 @@
         <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>200</v>
+        <v>-500</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1274,13 +1342,13 @@
         <v>200</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1291,46 +1359,52 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-4400</v>
+        <v>-4700</v>
       </c>
       <c r="E21" s="3">
-        <v>-6100</v>
+        <v>-4700</v>
       </c>
       <c r="F21" s="3">
-        <v>-8100</v>
+        <v>-5100</v>
       </c>
       <c r="G21" s="3">
-        <v>-6300</v>
+        <v>-6200</v>
       </c>
       <c r="H21" s="3">
-        <v>-13200</v>
+        <v>-8200</v>
       </c>
       <c r="I21" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-12500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-11400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-400</v>
       </c>
       <c r="M21" s="3">
         <v>-200</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
+      <c r="N21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-200</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
@@ -1341,31 +1415,37 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>300</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>600</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H22" s="3">
-        <v>200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>100</v>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K22" s="3">
         <v>100</v>
@@ -1376,11 +1456,11 @@
       <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
+      <c r="N22" s="3">
+        <v>200</v>
+      </c>
+      <c r="O22" s="3">
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
@@ -1391,46 +1471,52 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-8300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6600</v>
       </c>
-      <c r="H23" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-600</v>
       </c>
       <c r="M23" s="3">
         <v>-300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="N23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O23" s="3">
+        <v>-300</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1441,31 +1527,37 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1485,14 +1577,20 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,46 +1639,52 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-8300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6600</v>
       </c>
-      <c r="H26" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-600</v>
       </c>
       <c r="M26" s="3">
         <v>-300</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="N26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O26" s="3">
+        <v>-300</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1591,46 +1695,52 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-8300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6600</v>
       </c>
-      <c r="H27" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-12600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-600</v>
       </c>
       <c r="M27" s="3">
         <v>-300</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="N27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-300</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1641,8 +1751,14 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1807,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1735,14 +1857,20 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1919,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,22 +1975,28 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1900</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>300</v>
+        <v>1300</v>
       </c>
       <c r="G32" s="3">
-        <v>200</v>
+        <v>-700</v>
       </c>
       <c r="H32" s="3">
         <v>-300</v>
@@ -1865,7 +2005,7 @@
         <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -1874,13 +2014,13 @@
         <v>-200</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1891,46 +2031,52 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-8300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6600</v>
       </c>
-      <c r="H33" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K33" s="3">
         <v>-12600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-600</v>
       </c>
       <c r="M33" s="3">
         <v>-300</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="N33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-300</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -1941,8 +2087,14 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,46 +2143,52 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-8300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6600</v>
       </c>
-      <c r="H35" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K35" s="3">
         <v>-12600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-600</v>
       </c>
       <c r="M35" s="3">
         <v>-300</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="N35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-300</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -2041,52 +2199,58 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2096,8 +2260,14 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2286,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,41 +2308,43 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F41" s="3">
         <v>7100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>10900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>10900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>26000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>200</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2360,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2230,47 +2410,53 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="E43" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F43" s="3">
         <v>400</v>
       </c>
       <c r="G43" s="3">
+        <v>500</v>
+      </c>
+      <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
+        <v>400</v>
+      </c>
+      <c r="J43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,34 +2472,40 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E44" s="3">
         <v>500</v>
       </c>
       <c r="F44" s="3">
+        <v>600</v>
+      </c>
+      <c r="G44" s="3">
+        <v>500</v>
+      </c>
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -2324,52 +2516,58 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3">
+        <v>100</v>
+      </c>
+      <c r="K45" s="3">
+        <v>400</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2386,41 +2584,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F46" s="3">
         <v>9000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>12300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>18400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>26800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>300</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,31 +2640,37 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2480,47 +2690,53 @@
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F48" s="3">
         <v>3000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>500</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,31 +2752,37 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F49" s="3">
         <v>3400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3700</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>3</v>
@@ -2568,11 +2790,11 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -2580,14 +2802,20 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2864,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,16 +2920,22 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -2709,11 +2949,11 @@
       <c r="I52" s="3">
         <v>0</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2727,17 +2967,23 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,41 +3032,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F54" s="3">
         <v>15400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>17900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>20200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>27600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>700</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +3088,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +3114,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,41 +3136,43 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2400</v>
+        <v>1700</v>
       </c>
       <c r="E57" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,40 +3188,46 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F58" s="3">
         <v>5200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>7800</v>
       </c>
-      <c r="F58" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500</v>
-      </c>
       <c r="H58" s="3">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>1500</v>
       </c>
       <c r="J58" s="3">
-        <v>200</v>
+        <v>1300</v>
       </c>
       <c r="K58" s="3">
         <v>200</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
+        <v>200</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2976,41 +3244,47 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
+        <v>400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>1700</v>
       </c>
-      <c r="E59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,41 +3300,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F60" s="3">
         <v>9200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>11300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>700</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,41 +3356,47 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1200</v>
+        <v>2000</v>
       </c>
       <c r="E61" s="3">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="F61" s="3">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="G61" s="3">
-        <v>1700</v>
+        <v>2400</v>
       </c>
       <c r="H61" s="3">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="I61" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3126,41 +3412,47 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="F62" s="3">
-        <v>1900</v>
+        <v>700</v>
       </c>
       <c r="G62" s="3">
-        <v>1500</v>
+        <v>800</v>
       </c>
       <c r="H62" s="3">
         <v>900</v>
       </c>
       <c r="I62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3468,14 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3524,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3580,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,41 +3636,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F66" s="3">
         <v>12200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>14500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>14100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>9900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3692,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3718,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3770,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3826,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3540,14 +3876,20 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,41 +3938,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-48000</v>
+        <v>-80400</v>
       </c>
       <c r="E72" s="3">
-        <v>-43600</v>
+        <v>-80400</v>
       </c>
       <c r="F72" s="3">
-        <v>-38100</v>
+        <v>-69300</v>
       </c>
       <c r="G72" s="3">
-        <v>-30600</v>
+        <v>-64100</v>
       </c>
       <c r="H72" s="3">
-        <v>-25000</v>
+        <v>-57800</v>
       </c>
       <c r="I72" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="K72" s="3">
         <v>-14700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-6900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-2400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3994,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +4050,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +4106,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,41 +4162,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F76" s="3">
         <v>3200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>9700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>14100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>23800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-2400</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4218,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,52 +4274,58 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3951,46 +4335,52 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-8300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6600</v>
       </c>
-      <c r="H81" s="3">
-        <v>-13800</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="K81" s="3">
         <v>-12600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-11700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-600</v>
       </c>
       <c r="M81" s="3">
         <v>-300</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="N81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-300</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -4001,8 +4391,14 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,13 +4417,15 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>200</v>
@@ -4036,19 +4434,19 @@
         <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
@@ -4056,11 +4454,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4071,8 +4469,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4525,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4581,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4637,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4693,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,47 +4749,53 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-5100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-5700</v>
       </c>
-      <c r="H89" s="3">
-        <v>-8300</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-6500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4371,8 +4805,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,35 +4831,37 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-300</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-100</v>
       </c>
-      <c r="G91" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-400</v>
-      </c>
       <c r="I91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -4429,11 +4871,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4441,8 +4883,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4939,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,46 +4995,52 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-1400</v>
       </c>
-      <c r="H94" s="3">
-        <v>-400</v>
-      </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4591,8 +5051,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,31 +5077,33 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4661,8 +5129,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +5185,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5241,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,46 +5297,52 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>4600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>5400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>24100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>10600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
+      <c r="O100" s="3">
+        <v>0</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
@@ -4861,46 +5353,52 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-800</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -4911,47 +5409,53 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-6300</v>
       </c>
-      <c r="H102" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="K102" s="3">
         <v>17300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>8600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4959,6 +5463,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
   <si>
     <t>MYNZ</t>
   </si>
@@ -656,83 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -742,53 +743,59 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>200</v>
+      </c>
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
       <c r="I8" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J8" s="3">
         <v>200</v>
       </c>
       <c r="K8" s="3">
+        <v>300</v>
+      </c>
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
+        <v>200</v>
+      </c>
+      <c r="N8" s="3">
         <v>600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -798,8 +805,14 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -822,16 +835,16 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
       </c>
       <c r="L9" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="M9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N9" s="3">
         <v>400</v>
@@ -839,11 +852,11 @@
       <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="P9" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>200</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
@@ -854,22 +867,28 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>100</v>
+      </c>
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
@@ -878,28 +897,28 @@
         <v>100</v>
       </c>
       <c r="J10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
       </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>100</v>
+      </c>
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
@@ -910,8 +929,14 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,52 +957,54 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>3500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>2600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>400</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>300</v>
       </c>
       <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
+      <c r="P12" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>100</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
@@ -988,8 +1015,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,26 +1077,32 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>900</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1073,23 +1112,23 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1100,8 +1139,14 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1112,28 +1157,28 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
+        <v>200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>200</v>
+      </c>
+      <c r="H15" s="3">
         <v>300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
         <v>200</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
         <v>100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>100</v>
@@ -1141,11 +1186,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
@@ -1156,8 +1201,14 @@
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,53 +1226,55 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="F17" s="3">
         <v>5200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>5200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>6800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>5800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>8200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>6700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>8600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>12800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>12300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1231,52 +1284,58 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-6600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-5600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-6500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-8400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-12600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-700</v>
       </c>
       <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+      <c r="P18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-300</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
@@ -1287,8 +1346,14 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,37 +1374,39 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-500</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>200</v>
+        <v>-500</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
@@ -1348,13 +1415,13 @@
         <v>200</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1365,52 +1432,58 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-4700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-4700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-5100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-6200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-8200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-6400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-7900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-12500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-11400</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-400</v>
       </c>
       <c r="O21" s="3">
         <v>-200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="P21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-200</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
@@ -1421,37 +1494,43 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>200</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>600</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
         <v>300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>100</v>
-      </c>
-      <c r="L22" s="3">
-        <v>200</v>
       </c>
       <c r="M22" s="3">
         <v>100</v>
@@ -1462,11 +1541,11 @@
       <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>100</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
@@ -1477,52 +1556,58 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-5500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-5500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-6300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-6600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-12600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-600</v>
       </c>
       <c r="O23" s="3">
         <v>-300</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="P23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>-300</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
@@ -1533,8 +1618,14 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1559,11 +1650,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1583,14 +1674,20 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,52 +1742,58 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-5500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-5500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-5200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-6300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-8300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-6600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-8200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-12600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-600</v>
       </c>
       <c r="O26" s="3">
         <v>-300</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="P26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>-300</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
@@ -1701,52 +1804,58 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-5500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-5500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-8300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-6600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-8200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-12600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-600</v>
       </c>
       <c r="O27" s="3">
         <v>-300</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="P27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>-300</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
@@ -1757,8 +1866,14 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1928,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1863,14 +1984,20 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +2052,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,37 +2114,43 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>500</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>-200</v>
+        <v>500</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
@@ -2020,13 +2159,13 @@
         <v>-200</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2037,52 +2176,58 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-5500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-5500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-6300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-8300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-6600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-8200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-12600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-600</v>
       </c>
       <c r="O33" s="3">
         <v>-300</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="P33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>-300</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
@@ -2093,8 +2238,14 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,52 +2300,58 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-5500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-5500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-6300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-8300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-6600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-8200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-12600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-600</v>
       </c>
       <c r="O35" s="3">
         <v>-300</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="P35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>-300</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
@@ -2205,58 +2362,64 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2266,8 +2429,14 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2457,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,47 +2481,49 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F41" s="3">
         <v>1000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>10900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>10900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>26000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,8 +2539,14 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2416,53 +2595,59 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>200</v>
+      </c>
+      <c r="F43" s="3">
         <v>300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>300</v>
-      </c>
-      <c r="F43" s="3">
-        <v>400</v>
-      </c>
-      <c r="G43" s="3">
-        <v>500</v>
       </c>
       <c r="H43" s="3">
         <v>400</v>
       </c>
       <c r="I43" s="3">
+        <v>500</v>
+      </c>
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
+        <v>400</v>
+      </c>
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2478,40 +2663,46 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>400</v>
+      </c>
+      <c r="F44" s="3">
         <v>500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>600</v>
       </c>
       <c r="G44" s="3">
         <v>500</v>
       </c>
       <c r="H44" s="3">
+        <v>600</v>
+      </c>
+      <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
+      <c r="M44" s="3">
+        <v>0</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
@@ -2522,20 +2713,26 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2561,19 +2758,19 @@
         <v>100</v>
       </c>
       <c r="K45" s="3">
+        <v>100</v>
+      </c>
+      <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>0</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2590,47 +2787,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F46" s="3">
         <v>2400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>9000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>11000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>12100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>12300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>18400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>26800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>300</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,8 +2849,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2672,11 +2881,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2696,53 +2905,59 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F48" s="3">
         <v>2900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,37 +2973,43 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F49" s="3">
         <v>3200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3700</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2796,11 +3017,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2808,14 +3029,20 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +3097,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,8 +3159,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2937,11 +3176,11 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
@@ -2955,11 +3194,11 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2973,17 +3212,23 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,47 +3283,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F54" s="3">
         <v>8500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>15400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>17900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>19300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>27600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>10000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3345,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3373,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,47 +3397,49 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3194,46 +3455,52 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F58" s="3">
         <v>6200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>6200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>7800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1300</v>
-      </c>
-      <c r="K58" s="3">
-        <v>200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>200</v>
+      </c>
+      <c r="O58" s="3">
+        <v>200</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
@@ -3250,47 +3517,53 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
         <v>400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>400</v>
-      </c>
-      <c r="F59" s="3">
-        <v>500</v>
       </c>
       <c r="G59" s="3">
         <v>400</v>
       </c>
       <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
+        <v>400</v>
+      </c>
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3306,47 +3579,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="F60" s="3">
         <v>10000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>11300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>4200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3362,47 +3641,53 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>900</v>
+      </c>
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3418,47 +3703,53 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3">
         <v>900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3765,14 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3827,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3889,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,47 +3951,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F66" s="3">
         <v>12600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>14500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>14100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>9900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +4013,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +4041,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +4099,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +4161,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3882,14 +4217,20 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-      <c r="S70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,47 +4285,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-80400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-80400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-69300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-64100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-57800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-49600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-43000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-14700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-6900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-2400</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4347,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4409,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4471,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,47 +4533,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-4100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-4100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>9700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>23800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-2400</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4595,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,58 +4657,64 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4341,52 +4724,58 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-5500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-5500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-6300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-8300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-6600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-8200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-12600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-11700</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-300</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-600</v>
       </c>
       <c r="O81" s="3">
         <v>-300</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="P81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>-300</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
@@ -4397,8 +4786,14 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,8 +4814,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4428,31 +4825,31 @@
         <v>100</v>
       </c>
       <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>100</v>
@@ -4460,11 +4857,11 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4475,8 +4872,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4934,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4996,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +5058,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +5120,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,53 +5182,59 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-6500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4811,8 +5244,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,41 +5272,43 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-900</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -4877,11 +5318,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -4889,8 +5330,14 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5392,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,52 +5454,58 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-1400</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>1200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
         <v>0</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5057,8 +5516,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,8 +5544,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5105,11 +5572,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5135,8 +5602,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5664,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5726,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,52 +5788,58 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F100" s="3">
         <v>1300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>4600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>5400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>24100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>10600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
@@ -5359,52 +5850,58 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -5415,53 +5912,59 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-4900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>17300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>8600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,6 +5972,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MYNZ_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="92">
   <si>
     <t>MYNZ</t>
   </si>
@@ -760,20 +760,20 @@
       <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
-        <v>300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>300</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
-        <v>200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>300</v>
@@ -822,20 +822,20 @@
       <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="F9" s="3">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
-        <v>100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
+      <c r="I9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -884,20 +884,20 @@
       <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
-        <v>100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
+      <c r="I10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
@@ -970,20 +970,20 @@
       <c r="E12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1600</v>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3">
         <v>2000</v>
       </c>
-      <c r="I12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3500</v>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K12" s="3">
         <v>2600</v>
@@ -1094,11 +1094,11 @@
       <c r="E14" s="3">
         <v>900</v>
       </c>
-      <c r="F14" s="3">
-        <v>300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>300</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>-700</v>
@@ -1157,16 +1157,16 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1239,20 +1239,20 @@
       <c r="E17" s="3">
         <v>4500</v>
       </c>
-      <c r="F17" s="3">
-        <v>5200</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5200</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>6800</v>
       </c>
-      <c r="I17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="J17" s="3">
-        <v>8200</v>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>6700</v>
@@ -1301,20 +1301,20 @@
       <c r="E18" s="3">
         <v>-4300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-4900</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-4900</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-6600</v>
       </c>
-      <c r="I18" s="3">
-        <v>-5600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-7900</v>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>-6500</v>
@@ -1387,20 +1387,20 @@
       <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
-        <v>700</v>
-      </c>
-      <c r="J20" s="3">
-        <v>300</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
@@ -1450,19 +1450,19 @@
         <v>-4000</v>
       </c>
       <c r="F21" s="3">
-        <v>-4700</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-4700</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-5100</v>
       </c>
       <c r="I21" s="3">
-        <v>-6200</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
-        <v>-8200</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-6400</v>
@@ -1511,11 +1511,11 @@
       <c r="E22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
-        <v>300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>300</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H22" s="3">
         <v>600</v>
@@ -1573,20 +1573,20 @@
       <c r="E23" s="3">
         <v>-5300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-5500</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-5200</v>
       </c>
-      <c r="I23" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-8300</v>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>-6600</v>
@@ -1759,20 +1759,20 @@
       <c r="E26" s="3">
         <v>-5300</v>
       </c>
-      <c r="F26" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-5500</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-5200</v>
       </c>
-      <c r="I26" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-8300</v>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>-6600</v>
@@ -1821,20 +1821,20 @@
       <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="F27" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-5500</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-5200</v>
       </c>
-      <c r="I27" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-8300</v>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>-6600</v>
@@ -2131,20 +2131,20 @@
       <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-300</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
@@ -2193,20 +2193,20 @@
       <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="F33" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-5500</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-5200</v>
       </c>
-      <c r="I33" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-8300</v>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>-6600</v>
@@ -2317,20 +2317,20 @@
       <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="F35" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-5500</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-5200</v>
       </c>
-      <c r="I35" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-8300</v>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>-6600</v>
@@ -2494,20 +2494,20 @@
       <c r="E41" s="3">
         <v>6200</v>
       </c>
-      <c r="F41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1000</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>10900</v>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>10900</v>
@@ -2618,20 +2618,20 @@
       <c r="E43" s="3">
         <v>200</v>
       </c>
-      <c r="F43" s="3">
-        <v>300</v>
-      </c>
-      <c r="G43" s="3">
-        <v>300</v>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>400</v>
       </c>
-      <c r="I43" s="3">
-        <v>500</v>
-      </c>
-      <c r="J43" s="3">
-        <v>400</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>400</v>
@@ -2680,20 +2680,20 @@
       <c r="E44" s="3">
         <v>400</v>
       </c>
-      <c r="F44" s="3">
-        <v>500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>500</v>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H44" s="3">
         <v>600</v>
       </c>
-      <c r="I44" s="3">
-        <v>500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>400</v>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>300</v>
@@ -2742,20 +2742,20 @@
       <c r="E45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>100</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
@@ -2804,20 +2804,20 @@
       <c r="E46" s="3">
         <v>7800</v>
       </c>
-      <c r="F46" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G46" s="3">
-        <v>2400</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>9000</v>
       </c>
-      <c r="I46" s="3">
-        <v>11000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>12100</v>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>12300</v>
@@ -2928,20 +2928,20 @@
       <c r="E48" s="3">
         <v>2400</v>
       </c>
-      <c r="F48" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>2900</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>3000</v>
       </c>
-      <c r="I48" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>3500</v>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>3500</v>
@@ -2990,20 +2990,20 @@
       <c r="E49" s="3">
         <v>3000</v>
       </c>
-      <c r="F49" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3200</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>3400</v>
       </c>
-      <c r="I49" s="3">
-        <v>3500</v>
-      </c>
-      <c r="J49" s="3">
-        <v>3600</v>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>3700</v>
@@ -3185,11 +3185,11 @@
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3300,20 +3300,20 @@
       <c r="E54" s="3">
         <v>13200</v>
       </c>
-      <c r="F54" s="3">
-        <v>8500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>8500</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>15400</v>
       </c>
-      <c r="I54" s="3">
-        <v>17900</v>
-      </c>
-      <c r="J54" s="3">
-        <v>19300</v>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>19500</v>
@@ -3410,20 +3410,20 @@
       <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1700</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>2300</v>
       </c>
-      <c r="I57" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2700</v>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>1100</v>
@@ -3472,20 +3472,20 @@
       <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="F58" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>6200</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>5200</v>
       </c>
-      <c r="I58" s="3">
-        <v>7800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>6000</v>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>1500</v>
@@ -3534,20 +3534,20 @@
       <c r="E59" s="3">
         <v>700</v>
       </c>
-      <c r="F59" s="3">
-        <v>400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>400</v>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>500</v>
       </c>
-      <c r="I59" s="3">
-        <v>400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>400</v>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>2300</v>
@@ -3596,20 +3596,20 @@
       <c r="E60" s="3">
         <v>5900</v>
       </c>
-      <c r="F60" s="3">
-        <v>10000</v>
-      </c>
-      <c r="G60" s="3">
-        <v>10000</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="I60" s="3">
-        <v>11300</v>
-      </c>
-      <c r="J60" s="3">
-        <v>10700</v>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>6700</v>
@@ -3659,19 +3659,19 @@
         <v>900</v>
       </c>
       <c r="F61" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>2200</v>
       </c>
       <c r="I61" s="3">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
         <v>2200</v>
@@ -3720,20 +3720,20 @@
       <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
-        <v>600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>600</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
         <v>700</v>
       </c>
-      <c r="I62" s="3">
-        <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>900</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>1000</v>
@@ -3968,20 +3968,20 @@
       <c r="E66" s="3">
         <v>7200</v>
       </c>
-      <c r="F66" s="3">
-        <v>12600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>12600</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>12200</v>
       </c>
-      <c r="I66" s="3">
-        <v>14500</v>
-      </c>
-      <c r="J66" s="3">
-        <v>14100</v>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>9900</v>
@@ -4302,20 +4302,20 @@
       <c r="E72" s="3">
         <v>-91000</v>
       </c>
-      <c r="F72" s="3">
-        <v>-80400</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-80400</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>-69300</v>
       </c>
-      <c r="I72" s="3">
-        <v>-64100</v>
-      </c>
-      <c r="J72" s="3">
-        <v>-57800</v>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>-49600</v>
@@ -4550,20 +4550,20 @@
       <c r="E76" s="3">
         <v>6000</v>
       </c>
-      <c r="F76" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>-4100</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>3200</v>
       </c>
-      <c r="I76" s="3">
-        <v>3400</v>
-      </c>
-      <c r="J76" s="3">
-        <v>5200</v>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>9700</v>
@@ -4741,20 +4741,20 @@
       <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="F81" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-5500</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-5200</v>
       </c>
-      <c r="I81" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-8300</v>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>-6600</v>
@@ -4824,23 +4824,23 @@
       <c r="D83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
-        <v>100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5199,20 +5199,20 @@
       <c r="E89" s="3">
         <v>-4500</v>
       </c>
-      <c r="F89" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-4100</v>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
         <v>-4700</v>
       </c>
-      <c r="I89" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-5100</v>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3">
         <v>-5700</v>
@@ -5285,20 +5285,20 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>-900</v>
@@ -5471,20 +5471,20 @@
       <c r="E94" s="3">
         <v>100</v>
       </c>
-      <c r="F94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-100</v>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>-1400</v>
@@ -5805,20 +5805,20 @@
       <c r="E100" s="3">
         <v>7000</v>
       </c>
-      <c r="F100" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>1300</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
         <v>3500</v>
       </c>
-      <c r="I100" s="3">
-        <v>4600</v>
-      </c>
-      <c r="J100" s="3">
-        <v>5400</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>800</v>
@@ -5864,23 +5864,23 @@
       <c r="D101" s="3">
         <v>-800</v>
       </c>
-      <c r="E101" s="3">
-        <v>500</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-100</v>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5930,19 +5930,19 @@
         <v>2600</v>
       </c>
       <c r="F102" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
         <v>-2200</v>
       </c>
       <c r="I102" s="3">
-        <v>-1600</v>
+        <v>0</v>
       </c>
       <c r="J102" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>-6300</v>
